--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,15 +55,18 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>В6513КС</t>
   </si>
   <si>
     <t>В7225ВР</t>
   </si>
   <si>
+    <t>78970155027720238</t>
+  </si>
+  <si>
     <t>78970155027720246</t>
   </si>
   <si>
@@ -76,19 +76,10 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>15:09:00</t>
-  </si>
-  <si>
-    <t>10:29:00</t>
-  </si>
-  <si>
-    <t>3236576070 3236576070</t>
-  </si>
-  <si>
-    <t>3236721726 3236721726</t>
+    <t>10:04</t>
+  </si>
+  <si>
+    <t>14:06</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ИНВЕСТИЦИОННА ПОЛИТИКА</t>
@@ -511,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -520,17 +511,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -570,63 +560,57 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46252</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
       </c>
       <c r="F2">
-        <v>3.5</v>
-      </c>
-      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="H2" s="1">
+        <v>39.5</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="J2" s="1">
+        <v>40.25</v>
+      </c>
+      <c r="K2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="I2" s="1">
-        <v>5.355</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="K2" s="1">
-        <v>5.46</v>
-      </c>
-      <c r="L2" t="s">
-        <v>21</v>
+      <c r="L2">
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>43730</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
+        <v>254225</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
-        <v>46255</v>
+        <v>46279</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -635,36 +619,33 @@
         <v>19</v>
       </c>
       <c r="F3">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
+        <v>31.28</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.66</v>
       </c>
       <c r="H3" s="1">
-        <v>0.65</v>
+        <v>20.645</v>
       </c>
       <c r="I3" s="1">
-        <v>13</v>
+        <v>0.67</v>
       </c>
       <c r="J3" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K3" s="1">
-        <v>13.2</v>
-      </c>
-      <c r="L3" t="s">
+        <v>20.958</v>
+      </c>
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3">
+        <v>43980</v>
+      </c>
+      <c r="M3">
+        <v>259730</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="M3">
-        <v>43800</v>
-      </c>
-      <c r="N3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -672,82 +653,82 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:13">
       <c r="A7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:13">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="7">
-        <v>20</v>
+        <v>31.28</v>
       </c>
       <c r="C8" s="8">
         <v>1</v>
       </c>
       <c r="D8" s="9">
-        <v>0.65</v>
+        <v>0.66001</v>
       </c>
       <c r="E8" s="7">
-        <v>13</v>
+        <v>20.64</v>
       </c>
       <c r="F8" s="7">
-        <v>13.2</v>
+        <v>20.96</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="7">
-        <v>3.5</v>
+        <v>25</v>
       </c>
       <c r="C9" s="8">
         <v>1</v>
       </c>
       <c r="D9" s="9">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="E9" s="7">
-        <v>5.36</v>
+        <v>39.5</v>
       </c>
       <c r="F9" s="7">
-        <v>5.46</v>
+        <v>40.25</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:13">
       <c r="A10" s="10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B10" s="11">
-        <v>23.5</v>
+        <v>56.28</v>
       </c>
       <c r="C10" s="12">
         <v>2</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="11">
-        <v>18.36</v>
+        <v>60.14</v>
       </c>
       <c r="F10" s="11">
-        <v>18.66</v>
+        <v>61.21</v>
       </c>
     </row>
   </sheetData>
